--- a/data_extactor/batch_10_fa/trimmed/batch_0020_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0020_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | دید نزدیک | تجسم فضایی</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | تجسم</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | علوم تجربی | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | علوم | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکاران سازه، سطوح و سامانه‌های هواپیما | تکنسین‌های اویونیک | کارشناسان و تکنسین‌های کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی مکانیک</t>
+          <t>مهندسان هوافضا | مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی مکانیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | ریاضیات | سخن گفتن | نگارش | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | ریاضیات | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال ریاضی | دید نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | تجسم فضایی</t>
+          <t>استدلال قیاسی | استدلال ریاضی | بینایی نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | تجسم</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | مهندسان عمران | مدیران پروژه ساختمانی | بازرسان ساختمان و سازه | برآوردکنندگان هزینه و مترورها | سرپرستان کارگاه‌های ساختمانی و عمرانی | مهندسان حمل و نقل</t>
+          <t>نقشه‌کشان معماری و عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | کارشناسان برآورد هزینه و مترورها | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | مهندسان حمل‌ونقل و ترافیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های کالیبراسیون | مهندسان برق | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز رایانه | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | استدلال استقرایی | مرتب‌سازی اطلاعات | چابکی انگشتان | حساسیت به مسئله | استدلال قیاسی</t>
+          <t>دقت کنترل | بینایی نزدیک | استدلال استقرایی | ترتیب‌دهی اطلاعات | مهارت انگشتان | حساسیت به مسئله | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های کالیبراسیون | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان مکاترونیک | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان مکاترونیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | دید نزدیک | درک شفاهی | درک کتبی | استدلال استقرایی | حساسیت به مسئله | چابکی انگشتان</t>
+          <t>استدلال قیاسی | بینایی نزدیک | درک شفاهی | درک کتبی | استدلال استقرایی | حساسیت به مسئله | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌های ابزار CNC | برنامه‌نویسان ماشین‌های CNC | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان مکاترونیک | مهندسان رباتیک</t>
+          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان مکاترونیک | مهندسان رباتیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | سخن گفتن | علوم تجربی | نگارش | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | سخن گفتن | علوم | نگارش | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک شفاهی</t>
+          <t>درک کتبی | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان و مدیران احیای اراضی آلوده و سایت‌های صنعتی | بازرسان انطباق زیست‌محیطی | مهندسان محیط زیست | تکنسین‌های حفاظت محیط زیست و بهداشت محیط | دانشمندان و متخصصان محیط زیست و بهداشت محیط | تکنسین‌های هیدرولوژی | اپراتورهای تصفیه‌خانه‌ها و تأسیسات آب و فاضلاب</t>
+          <t>مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | بازرسان رعایت ضوابط زیست‌محیطی | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | تکنسین‌های آب‌شناسی و هیدرولوژی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن | نگارش | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | نگارش | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>استدلال استقرایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان صنایع | مدیران تولید صنعتی | مهندسان ساخت و تولید | کارشناسان و تکنسین‌های مهندسی مکانیک</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان صنایع | مدیران تولید صنعتی | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نگارش | علوم تجربی | شنیدن فعال | یادگیری فعال | نظارت | سخن گفتن | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | علوم | گوش دادن فعال | یادگیری فعال | نظارت | سخن گفتن | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | استدلال استقرایی | دید نزدیک</t>
+          <t>درک کتبی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | استدلال استقرایی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | دانشمندان علم مواد | مهندسان میکروسیستم | مهندسان نانوسیستم | تکنسین‌های فوتونیک</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان شیمی | تکنسین‌های شیمی | کارشناسان و دانشمندان علوم مواد | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان نانوسیستم‌ها | تکنسین‌های فوتونیک و اپتیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | ریاضیات | یادگیری فعال | نظارت | علوم تجربی</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | ریاضیات | یادگیری فعال | نظارت | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | دید نزدیک | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی</t>
+          <t>درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های مهندسی خودرو | کارشناسان و تکنسین‌های کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان ساخت و تولید | نقشه‌کشان مکانیک | مهندسان مکانیک</t>
+          <t>تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان تولید و ساخت | نقشه‌کشان مکانیک | مهندسان مکانیک</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
